--- a/site/StructureDefinition-uy-consulta-no-urgente.xlsx
+++ b/site/StructureDefinition-uy-consulta-no-urgente.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10240" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10240" uniqueCount="862">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -953,7 +953,10 @@
 </t>
   </si>
   <si>
-    <t>Información contextual del evento CNU</t>
+    <t>Información contextual del evento CNU — obligatorio porque es la única vía para la hora de firma del profesional</t>
+  </si>
+  <si>
+    <t>Información contextual del evento CNU. Obligatorio: es la única ubicación disponible en esta guía para la hora de firma del profesional (ver HCENEncounter.participant.period.start).</t>
   </si>
   <si>
     <t>Provides context for the composition and supports searching.</t>
@@ -1369,9 +1372,6 @@
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>8</t>
   </si>
   <si>
     <t>Secciones que componen el documento de CNU</t>
@@ -1724,15 +1724,6 @@
   </si>
   <si>
     <t>Composition.section:motivosConsulta.text</t>
-  </si>
-  <si>
-    <t>Contenido narrativo de la sección para interpretación humana</t>
-  </si>
-  <si>
-    <t>Contenido narrativo de la sección para interpretación humana, sin restricciones específicas respecto a su contenido, idioma o trazabilidad con los elementos de datos estructurados.</t>
-  </si>
-  <si>
-    <t>This profile does not constrain the narrative in regard to content, language, or traceability to data elements.</t>
   </si>
   <si>
     <t>ClinicalDocument/component/structuredBody/component/section[code/@code='10154-3']/text</t>
@@ -7059,7 +7050,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>301</v>
       </c>
@@ -7072,13 +7063,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
@@ -7093,11 +7084,11 @@
         <v>303</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -7161,27 +7152,27 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7204,19 +7195,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -7265,7 +7256,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>89</v>
@@ -7280,27 +7271,27 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7323,17 +7314,17 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -7382,7 +7373,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>89</v>
@@ -7397,27 +7388,27 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7443,13 +7434,13 @@
         <v>103</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7499,7 +7490,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>89</v>
@@ -7514,16 +7505,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -7531,10 +7522,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7560,13 +7551,13 @@
         <v>165</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7596,7 +7587,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -7614,7 +7605,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -7629,16 +7620,16 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -7646,10 +7637,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7672,19 +7663,19 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7733,7 +7724,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7754,10 +7745,10 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -7765,10 +7756,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7880,10 +7871,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7997,14 +7988,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -8026,16 +8017,16 @@
         <v>110</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -8084,7 +8075,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -8116,10 +8107,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8145,14 +8136,14 @@
         <v>165</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -8180,10 +8171,10 @@
         <v>211</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -8201,7 +8192,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>89</v>
@@ -8222,7 +8213,7 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -8233,10 +8224,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8259,17 +8250,17 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -8318,7 +8309,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -8339,7 +8330,7 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -8350,10 +8341,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8376,17 +8367,17 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -8435,7 +8426,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -8456,21 +8447,21 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8493,19 +8484,19 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -8554,7 +8545,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -8569,16 +8560,16 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -8586,10 +8577,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8612,16 +8603,16 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8671,7 +8662,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8692,10 +8683,10 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -8703,10 +8694,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8818,10 +8809,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8935,14 +8926,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8964,16 +8955,16 @@
         <v>110</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -9022,7 +9013,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -9054,10 +9045,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9083,13 +9074,13 @@
         <v>165</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9118,10 +9109,10 @@
         <v>211</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -9139,7 +9130,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>89</v>
@@ -9160,10 +9151,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -9171,10 +9162,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9197,13 +9188,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9254,7 +9245,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>89</v>
@@ -9275,10 +9266,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -9286,10 +9277,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9312,19 +9303,19 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -9373,7 +9364,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -9394,10 +9385,10 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -9405,10 +9396,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9520,10 +9511,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9637,14 +9628,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9666,16 +9657,16 @@
         <v>110</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -9724,7 +9715,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9756,10 +9747,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9785,13 +9776,13 @@
         <v>218</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9820,10 +9811,10 @@
         <v>155</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -9841,7 +9832,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9862,10 +9853,10 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -9873,10 +9864,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9899,13 +9890,13 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9956,7 +9947,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9977,10 +9968,10 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9988,10 +9979,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10014,13 +10005,13 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10071,7 +10062,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -10092,7 +10083,7 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>20</v>
@@ -10103,10 +10094,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10114,10 +10105,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>439</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -10129,7 +10120,7 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>440</v>
@@ -10184,7 +10175,7 @@
         <v>116</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -10455,7 +10446,7 @@
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10477,16 +10468,16 @@
         <v>110</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -10535,7 +10526,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10675,7 +10666,7 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>20</v>
@@ -10841,7 +10832,7 @@
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10911,13 +10902,13 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" hidden="true">
@@ -10948,7 +10939,7 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>466</v>
@@ -11420,7 +11411,7 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>492</v>
@@ -11750,7 +11741,7 @@
         <v>509</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>510</v>
@@ -11775,7 +11766,7 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>511</v>
@@ -11832,7 +11823,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -12103,7 +12094,7 @@
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -12125,16 +12116,16 @@
         <v>110</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -12183,7 +12174,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -12323,7 +12314,7 @@
         <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>20</v>
@@ -13780,7 +13771,7 @@
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13850,13 +13841,13 @@
         <v>20</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="93" hidden="true">
@@ -13887,7 +13878,7 @@
         <v>20</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>466</v>
@@ -13976,7 +13967,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
         <v>552</v>
       </c>
@@ -13995,7 +13986,7 @@
         <v>89</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>20</v>
@@ -14007,13 +13998,13 @@
         <v>176</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>553</v>
+        <v>470</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>555</v>
+        <v>472</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14078,7 +14069,7 @@
         <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>20</v>
@@ -14095,7 +14086,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>475</v>
@@ -14214,7 +14205,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>483</v>
@@ -14333,7 +14324,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>491</v>
@@ -14359,13 +14350,13 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>494</v>
@@ -14433,7 +14424,7 @@
         <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>20</v>
@@ -14450,7 +14441,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>497</v>
@@ -14569,7 +14560,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>505</v>
@@ -14686,13 +14677,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>20</v>
@@ -14714,10 +14705,10 @@
         <v>20</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>441</v>
@@ -14771,7 +14762,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14786,7 +14777,7 @@
         <v>443</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>20</v>
@@ -14803,7 +14794,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>445</v>
@@ -14918,7 +14909,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>446</v>
@@ -15035,14 +15026,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>447</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -15064,16 +15055,16 @@
         <v>110</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>20</v>
@@ -15122,7 +15113,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -15154,7 +15145,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>448</v>
@@ -15183,10 +15174,10 @@
         <v>103</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>452</v>
@@ -15202,7 +15193,7 @@
         <v>20</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>20</v>
@@ -15256,13 +15247,13 @@
         <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>20</v>
@@ -15273,7 +15264,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>454</v>
@@ -15302,10 +15293,10 @@
         <v>218</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>457</v>
@@ -15318,7 +15309,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>20</v>
@@ -15392,7 +15383,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>526</v>
@@ -15507,7 +15498,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>528</v>
@@ -15624,7 +15615,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>530</v>
@@ -15743,7 +15734,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>532</v>
@@ -15858,7 +15849,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>534</v>
@@ -15975,7 +15966,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>536</v>
@@ -16077,7 +16068,7 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>20</v>
@@ -16094,7 +16085,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>539</v>
@@ -16211,7 +16202,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>541</v>
@@ -16311,7 +16302,7 @@
         <v>101</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>20</v>
@@ -16328,7 +16319,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>544</v>
@@ -16428,7 +16419,7 @@
         <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>20</v>
@@ -16445,7 +16436,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>547</v>
@@ -16564,7 +16555,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>549</v>
@@ -16683,7 +16674,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>461</v>
@@ -16719,7 +16710,7 @@
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>20</v>
@@ -16789,18 +16780,18 @@
         <v>20</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>465</v>
@@ -16826,7 +16817,7 @@
         <v>20</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L118" t="s" s="2">
         <v>466</v>
@@ -16915,9 +16906,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>469</v>
@@ -16934,7 +16925,7 @@
         <v>89</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>20</v>
@@ -16946,13 +16937,13 @@
         <v>176</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>553</v>
+        <v>470</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>555</v>
+        <v>472</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -17017,7 +17008,7 @@
         <v>101</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>20</v>
@@ -17034,7 +17025,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>475</v>
@@ -17153,7 +17144,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>483</v>
@@ -17272,7 +17263,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>491</v>
@@ -17298,13 +17289,13 @@
         <v>20</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>494</v>
@@ -17372,7 +17363,7 @@
         <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>20</v>
@@ -17389,7 +17380,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>497</v>
@@ -17508,7 +17499,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>505</v>
@@ -17625,13 +17616,13 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>20</v>
@@ -17653,10 +17644,10 @@
         <v>20</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>441</v>
@@ -17710,7 +17701,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17725,7 +17716,7 @@
         <v>443</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>20</v>
@@ -17742,7 +17733,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>445</v>
@@ -17857,7 +17848,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>446</v>
@@ -17974,14 +17965,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>447</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -18003,16 +17994,16 @@
         <v>110</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>20</v>
@@ -18061,7 +18052,7 @@
         <v>20</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -18093,7 +18084,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>448</v>
@@ -18122,10 +18113,10 @@
         <v>103</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="N129" t="s" s="2">
         <v>452</v>
@@ -18141,7 +18132,7 @@
         <v>20</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>20</v>
@@ -18195,13 +18186,13 @@
         <v>101</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>20</v>
@@ -18212,7 +18203,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>454</v>
@@ -18241,10 +18232,10 @@
         <v>218</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>457</v>
@@ -18257,7 +18248,7 @@
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>20</v>
@@ -18331,7 +18322,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>526</v>
@@ -18446,7 +18437,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>528</v>
@@ -18563,7 +18554,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>530</v>
@@ -18682,7 +18673,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>532</v>
@@ -18797,7 +18788,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>534</v>
@@ -18914,7 +18905,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>536</v>
@@ -19016,7 +19007,7 @@
         <v>101</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>20</v>
@@ -19033,7 +19024,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>539</v>
@@ -19150,7 +19141,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>541</v>
@@ -19250,7 +19241,7 @@
         <v>101</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>20</v>
@@ -19267,7 +19258,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>544</v>
@@ -19367,7 +19358,7 @@
         <v>101</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>20</v>
@@ -19384,7 +19375,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>547</v>
@@ -19503,7 +19494,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>549</v>
@@ -19622,7 +19613,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>461</v>
@@ -19658,7 +19649,7 @@
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>20</v>
@@ -19728,18 +19719,18 @@
         <v>20</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>465</v>
@@ -19765,7 +19756,7 @@
         <v>20</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L143" t="s" s="2">
         <v>466</v>
@@ -19854,9 +19845,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>469</v>
@@ -19873,7 +19864,7 @@
         <v>89</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>20</v>
@@ -19885,13 +19876,13 @@
         <v>176</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>553</v>
+        <v>470</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>555</v>
+        <v>472</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19956,7 +19947,7 @@
         <v>101</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>20</v>
@@ -19973,7 +19964,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>475</v>
@@ -20092,7 +20083,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>483</v>
@@ -20211,7 +20202,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>491</v>
@@ -20237,13 +20228,13 @@
         <v>20</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="N147" t="s" s="2">
         <v>494</v>
@@ -20311,7 +20302,7 @@
         <v>101</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>20</v>
@@ -20328,7 +20319,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>497</v>
@@ -20447,7 +20438,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>505</v>
@@ -20564,13 +20555,13 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D150" t="s" s="2">
         <v>20</v>
@@ -20592,10 +20583,10 @@
         <v>20</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="M150" t="s" s="2">
         <v>441</v>
@@ -20649,7 +20640,7 @@
         <v>20</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -20664,7 +20655,7 @@
         <v>443</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>20</v>
@@ -20681,7 +20672,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>445</v>
@@ -20796,7 +20787,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>446</v>
@@ -20913,14 +20904,14 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>447</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -20942,16 +20933,16 @@
         <v>110</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N153" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>20</v>
@@ -21000,7 +20991,7 @@
         <v>20</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -21032,7 +21023,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>448</v>
@@ -21061,10 +21052,10 @@
         <v>103</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="N154" t="s" s="2">
         <v>452</v>
@@ -21080,7 +21071,7 @@
         <v>20</v>
       </c>
       <c r="S154" t="s" s="2">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="T154" t="s" s="2">
         <v>20</v>
@@ -21134,13 +21125,13 @@
         <v>101</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>20</v>
@@ -21151,7 +21142,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>454</v>
@@ -21180,10 +21171,10 @@
         <v>218</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>457</v>
@@ -21196,7 +21187,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>20</v>
@@ -21270,7 +21261,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>526</v>
@@ -21385,7 +21376,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>528</v>
@@ -21502,7 +21493,7 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>530</v>
@@ -21621,7 +21612,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>532</v>
@@ -21736,7 +21727,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>534</v>
@@ -21853,7 +21844,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>536</v>
@@ -21955,7 +21946,7 @@
         <v>101</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>20</v>
@@ -21972,7 +21963,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>539</v>
@@ -22089,7 +22080,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>541</v>
@@ -22189,7 +22180,7 @@
         <v>101</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>20</v>
@@ -22206,7 +22197,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>544</v>
@@ -22306,7 +22297,7 @@
         <v>101</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>20</v>
@@ -22323,7 +22314,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>547</v>
@@ -22442,7 +22433,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>549</v>
@@ -22561,7 +22552,7 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>461</v>
@@ -22597,7 +22588,7 @@
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>20</v>
@@ -22667,18 +22658,18 @@
         <v>20</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>465</v>
@@ -22704,7 +22695,7 @@
         <v>20</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L168" t="s" s="2">
         <v>466</v>
@@ -22793,9 +22784,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>469</v>
@@ -22812,7 +22803,7 @@
         <v>89</v>
       </c>
       <c r="H169" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I169" t="s" s="2">
         <v>20</v>
@@ -22824,13 +22815,13 @@
         <v>176</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>553</v>
+        <v>470</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>555</v>
+        <v>472</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -22895,7 +22886,7 @@
         <v>101</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>20</v>
@@ -22912,7 +22903,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>475</v>
@@ -23031,7 +23022,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>483</v>
@@ -23150,7 +23141,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>491</v>
@@ -23176,13 +23167,13 @@
         <v>20</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="N172" t="s" s="2">
         <v>494</v>
@@ -23250,7 +23241,7 @@
         <v>101</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>20</v>
@@ -23267,7 +23258,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>497</v>
@@ -23386,7 +23377,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>505</v>
@@ -23503,13 +23494,13 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D175" t="s" s="2">
         <v>20</v>
@@ -23531,10 +23522,10 @@
         <v>20</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="M175" t="s" s="2">
         <v>441</v>
@@ -23588,7 +23579,7 @@
         <v>20</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>78</v>
@@ -23603,7 +23594,7 @@
         <v>443</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>20</v>
@@ -23620,7 +23611,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>445</v>
@@ -23735,7 +23726,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>446</v>
@@ -23852,14 +23843,14 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>447</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
@@ -23881,16 +23872,16 @@
         <v>110</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N178" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>20</v>
@@ -23939,7 +23930,7 @@
         <v>20</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>78</v>
@@ -23971,7 +23962,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>448</v>
@@ -24000,10 +23991,10 @@
         <v>103</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="N179" t="s" s="2">
         <v>452</v>
@@ -24019,7 +24010,7 @@
         <v>20</v>
       </c>
       <c r="S179" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="T179" t="s" s="2">
         <v>20</v>
@@ -24073,13 +24064,13 @@
         <v>101</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="AL179" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>20</v>
@@ -24090,7 +24081,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>454</v>
@@ -24119,10 +24110,10 @@
         <v>218</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="N180" t="s" s="2">
         <v>457</v>
@@ -24135,7 +24126,7 @@
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>20</v>
@@ -24209,7 +24200,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>526</v>
@@ -24324,7 +24315,7 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>528</v>
@@ -24441,7 +24432,7 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>530</v>
@@ -24560,7 +24551,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>532</v>
@@ -24675,7 +24666,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>534</v>
@@ -24792,7 +24783,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>536</v>
@@ -24894,7 +24885,7 @@
         <v>101</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="AL186" t="s" s="2">
         <v>20</v>
@@ -24911,7 +24902,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>539</v>
@@ -25028,7 +25019,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>541</v>
@@ -25128,7 +25119,7 @@
         <v>101</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="AL188" t="s" s="2">
         <v>20</v>
@@ -25145,7 +25136,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>544</v>
@@ -25245,7 +25236,7 @@
         <v>101</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="AL189" t="s" s="2">
         <v>20</v>
@@ -25262,7 +25253,7 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>547</v>
@@ -25381,7 +25372,7 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>549</v>
@@ -25500,7 +25491,7 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>461</v>
@@ -25536,7 +25527,7 @@
       </c>
       <c r="N192" s="2"/>
       <c r="O192" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>20</v>
@@ -25606,18 +25597,18 @@
         <v>20</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>465</v>
@@ -25643,7 +25634,7 @@
         <v>20</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L193" t="s" s="2">
         <v>466</v>
@@ -25732,9 +25723,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>469</v>
@@ -25751,7 +25742,7 @@
         <v>89</v>
       </c>
       <c r="H194" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I194" t="s" s="2">
         <v>20</v>
@@ -25763,13 +25754,13 @@
         <v>176</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>553</v>
+        <v>470</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>555</v>
+        <v>472</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -25834,7 +25825,7 @@
         <v>101</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>20</v>
@@ -25851,7 +25842,7 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>475</v>
@@ -25970,7 +25961,7 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>483</v>
@@ -26089,7 +26080,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>491</v>
@@ -26115,13 +26106,13 @@
         <v>20</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="N197" t="s" s="2">
         <v>494</v>
@@ -26189,7 +26180,7 @@
         <v>101</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="AL197" t="s" s="2">
         <v>20</v>
@@ -26206,7 +26197,7 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>497</v>
@@ -26325,7 +26316,7 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>505</v>
@@ -26442,13 +26433,13 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D200" t="s" s="2">
         <v>20</v>
@@ -26470,10 +26461,10 @@
         <v>20</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="M200" t="s" s="2">
         <v>441</v>
@@ -26527,7 +26518,7 @@
         <v>20</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>78</v>
@@ -26542,7 +26533,7 @@
         <v>443</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="AL200" t="s" s="2">
         <v>20</v>
@@ -26559,7 +26550,7 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>445</v>
@@ -26674,7 +26665,7 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>446</v>
@@ -26791,14 +26782,14 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>447</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" t="s" s="2">
@@ -26820,16 +26811,16 @@
         <v>110</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N203" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>20</v>
@@ -26878,7 +26869,7 @@
         <v>20</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>78</v>
@@ -26910,7 +26901,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>448</v>
@@ -26939,10 +26930,10 @@
         <v>103</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="N204" t="s" s="2">
         <v>452</v>
@@ -26958,7 +26949,7 @@
         <v>20</v>
       </c>
       <c r="S204" t="s" s="2">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="T204" t="s" s="2">
         <v>20</v>
@@ -27012,13 +27003,13 @@
         <v>101</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN204" t="s" s="2">
         <v>20</v>
@@ -27029,7 +27020,7 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>454</v>
@@ -27058,10 +27049,10 @@
         <v>218</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="N205" t="s" s="2">
         <v>457</v>
@@ -27074,7 +27065,7 @@
       </c>
       <c r="Q205" s="2"/>
       <c r="R205" t="s" s="2">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="S205" t="s" s="2">
         <v>20</v>
@@ -27148,7 +27139,7 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>526</v>
@@ -27263,7 +27254,7 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>528</v>
@@ -27380,7 +27371,7 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>530</v>
@@ -27499,7 +27490,7 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>532</v>
@@ -27614,7 +27605,7 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>534</v>
@@ -27731,7 +27722,7 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>536</v>
@@ -27833,7 +27824,7 @@
         <v>101</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="AL211" t="s" s="2">
         <v>20</v>
@@ -27850,7 +27841,7 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>539</v>
@@ -27967,7 +27958,7 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>541</v>
@@ -28067,7 +28058,7 @@
         <v>101</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="AL213" t="s" s="2">
         <v>20</v>
@@ -28084,7 +28075,7 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>544</v>
@@ -28184,7 +28175,7 @@
         <v>101</v>
       </c>
       <c r="AK214" t="s" s="2">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="AL214" t="s" s="2">
         <v>20</v>
@@ -28201,7 +28192,7 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>547</v>
@@ -28320,7 +28311,7 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>549</v>
@@ -28439,7 +28430,7 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>461</v>
@@ -28475,7 +28466,7 @@
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>20</v>
@@ -28545,18 +28536,18 @@
         <v>20</v>
       </c>
       <c r="AM217" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN217" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO217" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>465</v>
@@ -28582,7 +28573,7 @@
         <v>20</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L218" t="s" s="2">
         <v>466</v>
@@ -28671,9 +28662,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>469</v>
@@ -28690,7 +28681,7 @@
         <v>89</v>
       </c>
       <c r="H219" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I219" t="s" s="2">
         <v>20</v>
@@ -28702,13 +28693,13 @@
         <v>176</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>553</v>
+        <v>470</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>555</v>
+        <v>472</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
@@ -28773,7 +28764,7 @@
         <v>101</v>
       </c>
       <c r="AK219" t="s" s="2">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="AL219" t="s" s="2">
         <v>20</v>
@@ -28790,7 +28781,7 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>475</v>
@@ -28909,7 +28900,7 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>483</v>
@@ -29028,7 +29019,7 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>491</v>
@@ -29054,13 +29045,13 @@
         <v>20</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="N222" t="s" s="2">
         <v>494</v>
@@ -29128,7 +29119,7 @@
         <v>101</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="AL222" t="s" s="2">
         <v>20</v>
@@ -29145,7 +29136,7 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>497</v>
@@ -29264,7 +29255,7 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>505</v>
@@ -29381,13 +29372,13 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D225" t="s" s="2">
         <v>20</v>
@@ -29409,10 +29400,10 @@
         <v>20</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="M225" t="s" s="2">
         <v>441</v>
@@ -29466,7 +29457,7 @@
         <v>20</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>78</v>
@@ -29481,7 +29472,7 @@
         <v>443</v>
       </c>
       <c r="AK225" t="s" s="2">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="AL225" t="s" s="2">
         <v>20</v>
@@ -29498,7 +29489,7 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>445</v>
@@ -29613,7 +29604,7 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>446</v>
@@ -29730,14 +29721,14 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>447</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
@@ -29759,16 +29750,16 @@
         <v>110</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N228" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O228" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>20</v>
@@ -29817,7 +29808,7 @@
         <v>20</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>78</v>
@@ -29849,7 +29840,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>448</v>
@@ -29878,10 +29869,10 @@
         <v>103</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="N229" t="s" s="2">
         <v>452</v>
@@ -29897,7 +29888,7 @@
         <v>20</v>
       </c>
       <c r="S229" t="s" s="2">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="T229" t="s" s="2">
         <v>20</v>
@@ -29951,13 +29942,13 @@
         <v>101</v>
       </c>
       <c r="AK229" t="s" s="2">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="AL229" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM229" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN229" t="s" s="2">
         <v>20</v>
@@ -29968,7 +29959,7 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>454</v>
@@ -29997,10 +29988,10 @@
         <v>218</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="N230" t="s" s="2">
         <v>457</v>
@@ -30013,7 +30004,7 @@
       </c>
       <c r="Q230" s="2"/>
       <c r="R230" t="s" s="2">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="S230" t="s" s="2">
         <v>20</v>
@@ -30087,7 +30078,7 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>526</v>
@@ -30202,7 +30193,7 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>528</v>
@@ -30319,7 +30310,7 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>530</v>
@@ -30438,7 +30429,7 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>532</v>
@@ -30553,7 +30544,7 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>534</v>
@@ -30670,7 +30661,7 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>536</v>
@@ -30772,7 +30763,7 @@
         <v>101</v>
       </c>
       <c r="AK236" t="s" s="2">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="AL236" t="s" s="2">
         <v>20</v>
@@ -30789,7 +30780,7 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>539</v>
@@ -30906,7 +30897,7 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>541</v>
@@ -31006,7 +30997,7 @@
         <v>101</v>
       </c>
       <c r="AK238" t="s" s="2">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="AL238" t="s" s="2">
         <v>20</v>
@@ -31023,7 +31014,7 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>544</v>
@@ -31123,7 +31114,7 @@
         <v>101</v>
       </c>
       <c r="AK239" t="s" s="2">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="AL239" t="s" s="2">
         <v>20</v>
@@ -31140,7 +31131,7 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>547</v>
@@ -31259,7 +31250,7 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>549</v>
@@ -31378,7 +31369,7 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>461</v>
@@ -31414,7 +31405,7 @@
       </c>
       <c r="N242" s="2"/>
       <c r="O242" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>20</v>
@@ -31484,18 +31475,18 @@
         <v>20</v>
       </c>
       <c r="AM242" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN242" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO242" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>465</v>
@@ -31521,7 +31512,7 @@
         <v>20</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L243" t="s" s="2">
         <v>466</v>
@@ -31610,9 +31601,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>469</v>
@@ -31629,7 +31620,7 @@
         <v>89</v>
       </c>
       <c r="H244" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I244" t="s" s="2">
         <v>20</v>
@@ -31641,13 +31632,13 @@
         <v>176</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>553</v>
+        <v>470</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>555</v>
+        <v>472</v>
       </c>
       <c r="O244" s="2"/>
       <c r="P244" t="s" s="2">
@@ -31712,7 +31703,7 @@
         <v>101</v>
       </c>
       <c r="AK244" t="s" s="2">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="AL244" t="s" s="2">
         <v>20</v>
@@ -31729,7 +31720,7 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>475</v>
@@ -31848,7 +31839,7 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>483</v>
@@ -31967,7 +31958,7 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>491</v>
@@ -31993,13 +31984,13 @@
         <v>20</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="N247" t="s" s="2">
         <v>494</v>
@@ -32067,7 +32058,7 @@
         <v>101</v>
       </c>
       <c r="AK247" t="s" s="2">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="AL247" t="s" s="2">
         <v>20</v>
@@ -32084,7 +32075,7 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>497</v>
@@ -32203,7 +32194,7 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>505</v>
@@ -32320,13 +32311,13 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D250" t="s" s="2">
         <v>20</v>
@@ -32348,10 +32339,10 @@
         <v>20</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="M250" t="s" s="2">
         <v>441</v>
@@ -32405,7 +32396,7 @@
         <v>20</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>78</v>
@@ -32420,7 +32411,7 @@
         <v>443</v>
       </c>
       <c r="AK250" t="s" s="2">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="AL250" t="s" s="2">
         <v>20</v>
@@ -32437,7 +32428,7 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>445</v>
@@ -32552,7 +32543,7 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>446</v>
@@ -32669,14 +32660,14 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>447</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E253" s="2"/>
       <c r="F253" t="s" s="2">
@@ -32698,16 +32689,16 @@
         <v>110</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N253" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O253" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P253" t="s" s="2">
         <v>20</v>
@@ -32756,7 +32747,7 @@
         <v>20</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>78</v>
@@ -32788,7 +32779,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>448</v>
@@ -32817,10 +32808,10 @@
         <v>103</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="N254" t="s" s="2">
         <v>452</v>
@@ -32836,7 +32827,7 @@
         <v>20</v>
       </c>
       <c r="S254" t="s" s="2">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="T254" t="s" s="2">
         <v>20</v>
@@ -32890,13 +32881,13 @@
         <v>101</v>
       </c>
       <c r="AK254" t="s" s="2">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="AL254" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM254" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN254" t="s" s="2">
         <v>20</v>
@@ -32907,7 +32898,7 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>454</v>
@@ -32936,10 +32927,10 @@
         <v>218</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="N255" t="s" s="2">
         <v>457</v>
@@ -32952,7 +32943,7 @@
       </c>
       <c r="Q255" s="2"/>
       <c r="R255" t="s" s="2">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="S255" t="s" s="2">
         <v>20</v>
@@ -33026,7 +33017,7 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>526</v>
@@ -33141,7 +33132,7 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>528</v>
@@ -33258,7 +33249,7 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>530</v>
@@ -33377,7 +33368,7 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>532</v>
@@ -33492,7 +33483,7 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>534</v>
@@ -33609,7 +33600,7 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>536</v>
@@ -33711,7 +33702,7 @@
         <v>101</v>
       </c>
       <c r="AK261" t="s" s="2">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="AL261" t="s" s="2">
         <v>20</v>
@@ -33728,7 +33719,7 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>539</v>
@@ -33845,7 +33836,7 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>541</v>
@@ -33945,7 +33936,7 @@
         <v>101</v>
       </c>
       <c r="AK263" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="AL263" t="s" s="2">
         <v>20</v>
@@ -33962,7 +33953,7 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>544</v>
@@ -34062,7 +34053,7 @@
         <v>101</v>
       </c>
       <c r="AK264" t="s" s="2">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="AL264" t="s" s="2">
         <v>20</v>
@@ -34079,7 +34070,7 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>547</v>
@@ -34198,7 +34189,7 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>549</v>
@@ -34317,7 +34308,7 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>461</v>
@@ -34353,7 +34344,7 @@
       </c>
       <c r="N267" s="2"/>
       <c r="O267" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P267" t="s" s="2">
         <v>20</v>
@@ -34423,18 +34414,18 @@
         <v>20</v>
       </c>
       <c r="AM267" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN267" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO267" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>465</v>
@@ -34460,7 +34451,7 @@
         <v>20</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L268" t="s" s="2">
         <v>466</v>
@@ -34549,9 +34540,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>469</v>
@@ -34568,7 +34559,7 @@
         <v>89</v>
       </c>
       <c r="H269" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I269" t="s" s="2">
         <v>20</v>
@@ -34580,13 +34571,13 @@
         <v>176</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>553</v>
+        <v>470</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="N269" t="s" s="2">
-        <v>555</v>
+        <v>472</v>
       </c>
       <c r="O269" s="2"/>
       <c r="P269" t="s" s="2">
@@ -34651,7 +34642,7 @@
         <v>101</v>
       </c>
       <c r="AK269" t="s" s="2">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="AL269" t="s" s="2">
         <v>20</v>
@@ -34668,7 +34659,7 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>475</v>
@@ -34787,7 +34778,7 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>483</v>
@@ -34906,7 +34897,7 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>491</v>
@@ -34932,13 +34923,13 @@
         <v>20</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="N272" t="s" s="2">
         <v>494</v>
@@ -35006,7 +34997,7 @@
         <v>101</v>
       </c>
       <c r="AK272" t="s" s="2">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="AL272" t="s" s="2">
         <v>20</v>
@@ -35023,7 +35014,7 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>497</v>
@@ -35142,7 +35133,7 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>505</v>
